--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.01526590184560483</v>
       </c>
       <c r="C2" t="n">
-        <v>12425544</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12425544</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>9594353</v>
+        <v>4691403</v>
       </c>
       <c r="L2" t="n">
-        <v>6141130</v>
+        <v>2934668</v>
       </c>
       <c r="M2" t="n">
-        <v>1692704</v>
+        <v>786519</v>
       </c>
       <c r="N2" t="n">
-        <v>116741</v>
+        <v>48178</v>
       </c>
       <c r="O2" t="n">
-        <v>966651</v>
+        <v>458774</v>
       </c>
       <c r="P2" t="n">
-        <v>371558</v>
+        <v>179344</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999957084655762</v>
+        <v>0.9999930858612061</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9780681133270264</v>
+        <v>0.9566615223884583</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9417956471443176</v>
+        <v>0.8987423777580261</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9184733033180237</v>
+        <v>0.8572245836257935</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8489390015602112</v>
+        <v>0.703955352306366</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9481236934661865</v>
+        <v>0.8999009132385254</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9649879336357117</v>
+        <v>0.9312410950660706</v>
       </c>
       <c r="X2" t="n">
-        <v>12425544</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12425544</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>9257922</v>
+        <v>4535637</v>
       </c>
       <c r="AG2" t="n">
-        <v>5602510</v>
+        <v>2682458</v>
       </c>
       <c r="AH2" t="n">
-        <v>1500791</v>
+        <v>705093</v>
       </c>
       <c r="AI2" t="n">
-        <v>103745</v>
+        <v>45132</v>
       </c>
       <c r="AJ2" t="n">
-        <v>876959</v>
+        <v>418529</v>
       </c>
       <c r="AK2" t="n">
-        <v>348888</v>
+        <v>168879</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9374659061431885</v>
+        <v>0.9185657501220703</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8742755651473999</v>
+        <v>0.8371988534927368</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8102678060531616</v>
+        <v>0.7613507509231567</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.5869390368461609</v>
+        <v>0.5106700658798218</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.8630568981170654</v>
+        <v>0.8237884044647217</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9026249051094055</v>
+        <v>0.8738299608230591</v>
       </c>
     </row>
     <row r="3">
@@ -795,13 +795,13 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>9594353</v>
+        <v>4691403</v>
       </c>
       <c r="E3" t="n">
-        <v>252594</v>
+        <v>224592</v>
       </c>
       <c r="F3" t="n">
-        <v>6999</v>
+        <v>6989</v>
       </c>
       <c r="G3" t="n">
         <v>1713</v>
@@ -813,109 +813,109 @@
         <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>19715203</v>
+        <v>9857585</v>
       </c>
       <c r="K3" t="n">
-        <v>22069917</v>
+        <v>10933091</v>
       </c>
       <c r="L3" t="n">
-        <v>25337748</v>
+        <v>12525607</v>
       </c>
       <c r="M3" t="n">
-        <v>30135182</v>
+        <v>15011213</v>
       </c>
       <c r="N3" t="n">
-        <v>31943007</v>
+        <v>15961587</v>
       </c>
       <c r="O3" t="n">
-        <v>31070850</v>
+        <v>15510699</v>
       </c>
       <c r="P3" t="n">
-        <v>31740774</v>
+        <v>15863876</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9734784960746765</v>
+        <v>0.9526116847991943</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9560379981994629</v>
+        <v>0.9130446910858154</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9123278856277466</v>
+        <v>0.8473703861236572</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6594791412353516</v>
+        <v>0.5440645217895508</v>
       </c>
       <c r="V3" t="n">
-        <v>0.950436532497406</v>
+        <v>0.9019088745117188</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9612283110618591</v>
+        <v>0.9278877377510071</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9257922</v>
+        <v>4535637</v>
       </c>
       <c r="Z3" t="n">
-        <v>557637</v>
+        <v>363917</v>
       </c>
       <c r="AA3" t="n">
-        <v>23072</v>
+        <v>14825</v>
       </c>
       <c r="AB3" t="n">
-        <v>16910</v>
+        <v>10241</v>
       </c>
       <c r="AC3" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AD3" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="AE3" t="n">
-        <v>19715256</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>21667504</v>
+        <v>10743519</v>
       </c>
       <c r="AG3" t="n">
-        <v>24911615</v>
+        <v>12334615</v>
       </c>
       <c r="AH3" t="n">
-        <v>29934007</v>
+        <v>14921197</v>
       </c>
       <c r="AI3" t="n">
-        <v>31890769</v>
+        <v>15938602</v>
       </c>
       <c r="AJ3" t="n">
-        <v>30984591</v>
+        <v>15472205</v>
       </c>
       <c r="AK3" t="n">
-        <v>31716617</v>
+        <v>15852734</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9393429756164551</v>
+        <v>0.9209826588630676</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8721867799758911</v>
+        <v>0.8345761895179749</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8088912963867188</v>
+        <v>0.759644627571106</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.5860637426376343</v>
+        <v>0.5096666216850281</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.8622490167617798</v>
+        <v>0.822790801525116</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9025805592536926</v>
+        <v>0.8737440705299377</v>
       </c>
     </row>
     <row r="4">
@@ -929,16 +929,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>200921</v>
+        <v>198522</v>
       </c>
       <c r="E4" t="n">
-        <v>6141130</v>
+        <v>2934668</v>
       </c>
       <c r="F4" t="n">
-        <v>78312</v>
+        <v>77814</v>
       </c>
       <c r="G4" t="n">
-        <v>1921</v>
+        <v>1915</v>
       </c>
       <c r="H4" t="n">
         <v>1178</v>
@@ -947,109 +947,109 @@
         <v>56</v>
       </c>
       <c r="J4" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K4" t="n">
-        <v>215141</v>
+        <v>212529</v>
       </c>
       <c r="L4" t="n">
-        <v>379531</v>
+        <v>330637</v>
       </c>
       <c r="M4" t="n">
-        <v>150250</v>
+        <v>130999</v>
       </c>
       <c r="N4" t="n">
-        <v>20773</v>
+        <v>20261</v>
       </c>
       <c r="O4" t="n">
-        <v>52890</v>
+        <v>51031</v>
       </c>
       <c r="P4" t="n">
-        <v>13481</v>
+        <v>13242</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999978542327881</v>
+        <v>0.999996542930603</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9757679104804993</v>
+        <v>0.9546323418617249</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9488633871078491</v>
+        <v>0.9058370590209961</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9153902530670166</v>
+        <v>0.8522689938545227</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7423108220100403</v>
+        <v>0.6137676239013672</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9492786526679993</v>
+        <v>0.9009038209915161</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9631044864654541</v>
+        <v>0.9295613765716553</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>581677</v>
+        <v>380423</v>
       </c>
       <c r="Z4" t="n">
-        <v>5602510</v>
+        <v>2682458</v>
       </c>
       <c r="AA4" t="n">
-        <v>217409</v>
+        <v>135949</v>
       </c>
       <c r="AB4" t="n">
-        <v>14377</v>
+        <v>8964</v>
       </c>
       <c r="AC4" t="n">
-        <v>7078</v>
+        <v>5960</v>
       </c>
       <c r="AD4" t="n">
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>617554</v>
+        <v>402101</v>
       </c>
       <c r="AG4" t="n">
-        <v>805664</v>
+        <v>521629</v>
       </c>
       <c r="AH4" t="n">
-        <v>351425</v>
+        <v>221015</v>
       </c>
       <c r="AI4" t="n">
-        <v>73011</v>
+        <v>43246</v>
       </c>
       <c r="AJ4" t="n">
-        <v>139149</v>
+        <v>89525</v>
       </c>
       <c r="AK4" t="n">
-        <v>37638</v>
+        <v>24384</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9384034872055054</v>
+        <v>0.9197726845741272</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.8732299208641052</v>
+        <v>0.8358854055404663</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8095789551734924</v>
+        <v>0.7604967355728149</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.5865010619163513</v>
+        <v>0.5101678967475891</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.8626527786254883</v>
+        <v>0.8232892751693726</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9026026725769043</v>
+        <v>0.873786985874176</v>
       </c>
     </row>
     <row r="5">
@@ -1059,19 +1059,19 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7992</v>
+        <v>7854</v>
       </c>
       <c r="E5" t="n">
-        <v>115713</v>
+        <v>95079</v>
       </c>
       <c r="F5" t="n">
-        <v>1692704</v>
+        <v>786519</v>
       </c>
       <c r="G5" t="n">
-        <v>9158</v>
+        <v>8941</v>
       </c>
       <c r="H5" t="n">
-        <v>29191</v>
+        <v>29185</v>
       </c>
       <c r="I5" t="n">
         <v>606</v>
@@ -1080,106 +1080,106 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>261389</v>
+        <v>233377</v>
       </c>
       <c r="L5" t="n">
-        <v>282391</v>
+        <v>279488</v>
       </c>
       <c r="M5" t="n">
-        <v>162664</v>
+        <v>141669</v>
       </c>
       <c r="N5" t="n">
-        <v>60279</v>
+        <v>40374</v>
       </c>
       <c r="O5" t="n">
-        <v>50409</v>
+        <v>49896</v>
       </c>
       <c r="P5" t="n">
-        <v>14987</v>
+        <v>13938</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999983310699463</v>
+        <v>0.9999973177909851</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9851737022399902</v>
+        <v>0.9722529649734497</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9794055819511414</v>
+        <v>0.9620342254638672</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9902642965316772</v>
+        <v>0.9830328822135925</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9974782466888428</v>
+        <v>0.9962269067764282</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9967860579490662</v>
+        <v>0.9937196969985962</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9991142749786377</v>
+        <v>0.9983087182044983</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>20020</v>
+        <v>12213</v>
       </c>
       <c r="Z5" t="n">
-        <v>227430</v>
+        <v>143254</v>
       </c>
       <c r="AA5" t="n">
-        <v>1500791</v>
+        <v>705093</v>
       </c>
       <c r="AB5" t="n">
-        <v>23338</v>
+        <v>13468</v>
       </c>
       <c r="AC5" t="n">
-        <v>80709</v>
+        <v>51713</v>
       </c>
       <c r="AD5" t="n">
-        <v>3080</v>
+        <v>2447</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>597820</v>
+        <v>389143</v>
       </c>
       <c r="AG5" t="n">
-        <v>821011</v>
+        <v>531698</v>
       </c>
       <c r="AH5" t="n">
-        <v>354577</v>
+        <v>223095</v>
       </c>
       <c r="AI5" t="n">
-        <v>73275</v>
+        <v>43420</v>
       </c>
       <c r="AJ5" t="n">
-        <v>140101</v>
+        <v>90141</v>
       </c>
       <c r="AK5" t="n">
-        <v>37657</v>
+        <v>24403</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9621859192848206</v>
+        <v>0.9507638812065125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9493891000747681</v>
+        <v>0.9344554543495178</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9780340790748596</v>
+        <v>0.9723647236824036</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9954485893249512</v>
+        <v>0.9946070909500122</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9913116693496704</v>
+        <v>0.9888200759887695</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9976573586463928</v>
+        <v>0.996964156627655</v>
       </c>
     </row>
     <row r="6">
@@ -1189,22 +1189,22 @@
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>6199</v>
+        <v>6124</v>
       </c>
       <c r="E6" t="n">
-        <v>10313</v>
+        <v>10055</v>
       </c>
       <c r="F6" t="n">
-        <v>34978</v>
+        <v>16253</v>
       </c>
       <c r="G6" t="n">
-        <v>116741</v>
+        <v>48178</v>
       </c>
       <c r="H6" t="n">
-        <v>8204</v>
+        <v>7367</v>
       </c>
       <c r="I6" t="n">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>15763</v>
+        <v>9406</v>
       </c>
       <c r="Z6" t="n">
-        <v>14260</v>
+        <v>9011</v>
       </c>
       <c r="AA6" t="n">
-        <v>25613</v>
+        <v>14794</v>
       </c>
       <c r="AB6" t="n">
-        <v>103745</v>
+        <v>45132</v>
       </c>
       <c r="AC6" t="n">
-        <v>16279</v>
+        <v>9330</v>
       </c>
       <c r="AD6" t="n">
-        <v>1360</v>
+        <v>879</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1269,16 +1269,16 @@
         <v>815</v>
       </c>
       <c r="F7" t="n">
-        <v>29630</v>
+        <v>29619</v>
       </c>
       <c r="G7" t="n">
-        <v>7729</v>
+        <v>7456</v>
       </c>
       <c r="H7" t="n">
-        <v>966651</v>
+        <v>458774</v>
       </c>
       <c r="I7" t="n">
-        <v>12224</v>
+        <v>11995</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>6022</v>
+        <v>5213</v>
       </c>
       <c r="AA7" t="n">
-        <v>83790</v>
+        <v>54236</v>
       </c>
       <c r="AB7" t="n">
-        <v>17623</v>
+        <v>10075</v>
       </c>
       <c r="AC7" t="n">
-        <v>876959</v>
+        <v>418529</v>
       </c>
       <c r="AD7" t="n">
-        <v>32644</v>
+        <v>20602</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>22</v>
@@ -1343,16 +1343,16 @@
         <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G8" t="n">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="H8" t="n">
-        <v>14263</v>
+        <v>13247</v>
       </c>
       <c r="I8" t="n">
-        <v>371558</v>
+        <v>179344</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="Z8" t="n">
-        <v>315</v>
+        <v>234</v>
       </c>
       <c r="AA8" t="n">
-        <v>1541</v>
+        <v>1211</v>
       </c>
       <c r="AB8" t="n">
-        <v>763</v>
+        <v>498</v>
       </c>
       <c r="AC8" t="n">
-        <v>34966</v>
+        <v>22416</v>
       </c>
       <c r="AD8" t="n">
-        <v>348888</v>
+        <v>168879</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
